--- a/excel/WindImportExample.xlsx
+++ b/excel/WindImportExample.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PSTG Project 2026\Example Import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp-vonconnect\htdocs\windproject\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5844"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -98,7 +98,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="00.000000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -155,7 +155,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -545,7 +545,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
